--- a/Simulations_and_Calc/BC_Type3/LTSpice/dcm_calc.xlsx
+++ b/Simulations_and_Calc/BC_Type3/LTSpice/dcm_calc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FHTW_Daniel_Stevic\Masterarbeit\Dimensionierung_und_Simulation\BC_Type3\LTSpice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6644C3-7B12-4C50-8588-1092A99E5DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D56C7C-CC31-47DE-AE27-3FD5F18C0233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -111,7 +111,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,139 +361,139 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0210572069210717</c:v>
+                  <c:v>1.0417014457169653</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0818856381964599</c:v>
+                  <c:v>1.158564837949082</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1770852010246136</c:v>
+                  <c:v>1.3349341602570302</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3010409635747446</c:v>
+                  <c:v>1.5588131730962378</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4494465068352362</c:v>
+                  <c:v>1.8235990231180059</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6194637478740994</c:v>
+                  <c:v>2.1262039133007273</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.8093744462085373</c:v>
+                  <c:v>2.4654230829492185</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0182058805002976</c:v>
+                  <c:v>2.84100508156655</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.2454560957750882</c:v>
+                  <c:v>3.2531663593572722</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.4909141662866023</c:v>
+                  <c:v>3.7023393565155454</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7545468460991565</c:v>
+                  <c:v>4.1890403644633087</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.0364275503232916</c:v>
+                  <c:v>4.7138000369698672</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.3366916522379588</c:v>
+                  <c:v>5.2771276120905464</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.6555081538581038</c:v>
+                  <c:v>5.8794936973779865</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.9930616616098176</c:v>
+                  <c:v>6.521323391474553</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.3495409450357823</c:v>
+                  <c:v>7.2029951267339349</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.7251317618853435</c:v>
+                  <c:v>7.9248425818200712</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.1200124808325365</c:v>
+                  <c:v>8.6871581223150045</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.5343515527420681</c:v>
+                  <c:v>9.4901968726569734</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.9683062062900349</c:v>
+                  <c:v>10.334180906150753</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.4220219511926198</c:v>
+                  <c:v>11.219303270248957</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.8956326075225718</c:v>
+                  <c:v>12.14573170305537</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.3892606694363563</c:v>
+                  <c:v>13.11361197979598</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.9030178723229181</c:v>
+                  <c:v>14.123070876323018</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.437005873940203</c:v>
+                  <c:v>15.174218763754375</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>8.9913169888567257</c:v>
+                  <c:v>16.267151862324532</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9.5660349355481671</c:v>
+                  <c:v>17.401954188592264</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>10.161235569508495</c:v>
+                  <c:v>18.578699231558101</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10.776987585534668</c:v>
+                  <c:v>19.797451392022275</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>11.413353179175537</c:v>
+                  <c:v>21.05826721692047</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>12.070388662062026</c:v>
+                  <c:v>22.361196457177506</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>12.748145029064807</c:v>
+                  <c:v>23.706282974273009</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>13.446668477388794</c:v>
+                  <c:v>25.093565517475422</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>14.166000879119942</c:v>
+                  <c:v>26.523078390706893</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>14.906180209610721</c:v>
+                  <c:v>27.994852025310852</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>15.667240934586561</c:v>
+                  <c:v>29.50891347262257</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>16.449214359091258</c:v>
+                  <c:v>31.065286828179651</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>17.252128941448689</c:v>
+                  <c:v>32.663993597632341</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>18.076010575359618</c:v>
+                  <c:v>34.305053012892074</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>18.920882843119436</c:v>
+                  <c:v>35.988482305761558</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>19.786767242764668</c:v>
+                  <c:v>37.714296945189908</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>20.673683391754402</c:v>
+                  <c:v>39.48251084336583</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>21.581649209581656</c:v>
+                  <c:v>41.29313653507397</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>22.510681081499328</c:v>
+                  <c:v>43.14618533407517</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>23.460794005341434</c:v>
+                  <c:v>45.041667469709225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1550,6 +1549,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,62 +1606,62 @@
       <c r="G3" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H3" s="6">
-        <v>500</v>
-      </c>
-      <c r="I3" s="6">
+      <c r="H3">
+        <v>1000</v>
+      </c>
+      <c r="I3">
         <f>(H3*E3)/G3</f>
-        <v>106.38297872340426</v>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>C4/B4</f>
-        <v>1.4982785406685661</v>
+        <v>1.8235990231180057</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
       <c r="C4" s="3">
         <f>2*D4-B4</f>
-        <v>17.979342488022795</v>
+        <v>21.883188277416068</v>
       </c>
       <c r="D4" s="2">
         <f>(3*B4*G4+(F4^2)*E4*B4*H4+SQRT(((3*B4*G4+(F4^2)*E4*B4*H4)^2)-8*(B4^2)*(G4^2)))/(4*G4)</f>
-        <v>14.989671244011397</v>
+        <v>16.941594138708034</v>
       </c>
       <c r="E4" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F4">
-        <v>5.2999999999999999E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G4" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H4" s="6">
-        <v>500</v>
+      <c r="H4">
+        <v>1000</v>
       </c>
       <c r="I4" s="1">
         <f>(H4*E4)/G4</f>
-        <v>106.38297872340426</v>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" ref="A5:A12" si="0">C5/B5</f>
-        <v>2.4909139117464623</v>
+        <f t="shared" ref="A5:A11" si="0">C5/B5</f>
+        <v>3.7023393565155458</v>
       </c>
       <c r="B5">
         <v>12</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" ref="C5:C12" si="1">2*D5-$B$4</f>
-        <v>29.890966940957547</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ref="D5:D12" si="2">(3*B5*G5+(F5^2)*E5*B5*H5+SQRT(((3*B5*G5+(F5^2)*E5*B5*H5)^2)-8*(B5^2)*(G5^2)))/(4*G5)</f>
-        <v>20.945483470478774</v>
+        <f t="shared" ref="C5:C11" si="1">2*D5-$B$4</f>
+        <v>44.428072278186548</v>
+      </c>
+      <c r="D5" s="2">
+        <f>(3*B5*G5+(F5^2)*E5*B5*H5+SQRT(((3*B5*G5+(F5^2)*E5*B5*H5)^2)-8*(B5^2)*(G5^2)))/(4*G5)</f>
+        <v>28.214036139093274</v>
       </c>
       <c r="E5" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1672,29 +1672,29 @@
       <c r="G5" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H5" s="6">
-        <v>500</v>
-      </c>
-      <c r="I5" s="6">
-        <f t="shared" ref="I4:I12" si="3">(H5*E5)/G5</f>
-        <v>106.38297872340426</v>
+      <c r="H5">
+        <v>1000</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I12" si="2">(H5*E5)/G5</f>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>3.9930611411324164</v>
+        <v>6.521323391474553</v>
       </c>
       <c r="B6">
         <v>12</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="1"/>
-        <v>47.916733693588995</v>
+        <v>78.255880697694636</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
-        <v>29.958366846794497</v>
+        <f t="shared" ref="D6:D11" si="3">(3*B6*G6+(F6^2)*E6*B6*H6+SQRT(((3*B6*G6+(F6^2)*E6*B6*H6)^2)-8*(B6^2)*(G6^2)))/(4*G6)</f>
+        <v>45.127940348847318</v>
       </c>
       <c r="E6" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1705,29 +1705,29 @@
       <c r="G6" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H6" s="6">
-        <v>500</v>
-      </c>
-      <c r="I6" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H6">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>5.9683053186663484</v>
+        <v>10.334180906150754</v>
       </c>
       <c r="B7">
         <v>12</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="1"/>
-        <v>71.619663823996177</v>
+        <v>124.01017087380905</v>
       </c>
       <c r="D7">
-        <f t="shared" si="2"/>
-        <v>41.809831911998089</v>
+        <f t="shared" si="3"/>
+        <v>68.005085436904523</v>
       </c>
       <c r="E7" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1738,29 +1738,29 @@
       <c r="G7" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H7" s="6">
-        <v>500</v>
-      </c>
-      <c r="I7" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H7">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>8.4370045136031884</v>
+        <v>15.174218763754377</v>
       </c>
       <c r="B8">
         <v>12</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="1"/>
-        <v>101.24405416323826</v>
+        <v>182.09062516505253</v>
       </c>
       <c r="D8">
-        <f t="shared" si="2"/>
-        <v>56.62202708161913</v>
+        <f t="shared" si="3"/>
+        <v>97.045312582526265</v>
       </c>
       <c r="E8" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1771,29 +1771,29 @@
       <c r="G8" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H8" s="6">
-        <v>500</v>
-      </c>
-      <c r="I8" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H8">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>11.413351239101083</v>
+        <v>21.058267216920473</v>
       </c>
       <c r="B9">
         <v>12</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="1"/>
-        <v>136.96021486921299</v>
+        <v>252.6992066030457</v>
       </c>
       <c r="D9">
-        <f t="shared" si="2"/>
-        <v>74.480107434606495</v>
+        <f t="shared" si="3"/>
+        <v>132.34960330152285</v>
       </c>
       <c r="E9" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1804,29 +1804,29 @@
       <c r="G9" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H9" s="6">
-        <v>500</v>
-      </c>
-      <c r="I9" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>14.906177582460289</v>
+        <v>27.994852025310852</v>
       </c>
       <c r="B10">
         <v>12</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="1"/>
-        <v>178.87413098952348</v>
+        <v>335.93822430373024</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
-        <v>95.43706549476174</v>
+        <f t="shared" si="3"/>
+        <v>173.96911215186512</v>
       </c>
       <c r="E10" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1837,29 +1837,29 @@
       <c r="G10" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H10" s="6">
-        <v>500</v>
-      </c>
-      <c r="I10" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H10">
+        <v>1000</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>18.920879421620473</v>
+        <v>35.988482305761565</v>
       </c>
       <c r="B11">
         <v>12</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="1"/>
-        <v>227.05055305944566</v>
+        <v>431.86178766913878</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
-        <v>119.52527652972283</v>
+        <f t="shared" si="3"/>
+        <v>221.93089383456939</v>
       </c>
       <c r="E11" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1870,29 +1870,29 @@
       <c r="G11" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H11" s="6">
-        <v>500</v>
-      </c>
-      <c r="I11" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>C12/B12</f>
-        <v>23.460789682380717</v>
+        <v>45.041667469709218</v>
       </c>
       <c r="B12">
         <v>12</v>
       </c>
       <c r="C12" s="4">
         <f>2*D12-$B$4</f>
-        <v>281.52947618856859</v>
+        <v>540.50000963651064</v>
       </c>
       <c r="D12" s="2">
         <f>(3*B12*G12+(F12^2)*E12*B12*H12+SQRT(((3*B12*G12+(F12^2)*E12*B12*H12)^2)-8*(B12^2)*(G12^2)))/(4*G12)</f>
-        <v>146.7647380942843</v>
+        <v>276.25000481825532</v>
       </c>
       <c r="E12" s="1">
         <v>1.0000000000000001E-5</v>
@@ -1903,12 +1903,12 @@
       <c r="G12" s="2">
         <v>4.6999999999999997E-5</v>
       </c>
-      <c r="H12" s="6">
-        <v>500</v>
-      </c>
-      <c r="I12" s="6">
-        <f t="shared" si="3"/>
-        <v>106.38297872340426</v>
+      <c r="H12">
+        <v>1000</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -1931,13 +1931,13 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>106.383</v>
+        <v>212.76595744680853</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
-        <f t="shared" ref="B23:B67" si="4">1/2+(1/2)*C23^2*$D$22+(1/2)*SQRT(1+6*C23^2*$D$22+(C23^4)*$D$22^2)</f>
-        <v>1.0210572069210717</v>
+        <f t="shared" ref="B23:B66" si="4">1/2+(1/2)*C23^2*$D$22+(1/2)*SQRT(1+6*C23^2*$D$22+(C23^4)*$D$22^2)</f>
+        <v>1.0417014457169653</v>
       </c>
       <c r="C23">
         <v>0.01</v>
@@ -1946,7 +1946,7 @@
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
         <f t="shared" si="4"/>
-        <v>1.0818856381964599</v>
+        <v>1.158564837949082</v>
       </c>
       <c r="C24">
         <v>0.02</v>
@@ -1955,7 +1955,7 @@
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
         <f t="shared" si="4"/>
-        <v>1.1770852010246136</v>
+        <v>1.3349341602570302</v>
       </c>
       <c r="C25">
         <v>0.03</v>
@@ -1964,7 +1964,7 @@
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
         <f t="shared" si="4"/>
-        <v>1.3010409635747446</v>
+        <v>1.5588131730962378</v>
       </c>
       <c r="C26">
         <v>0.04</v>
@@ -1973,7 +1973,7 @@
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27">
         <f t="shared" si="4"/>
-        <v>1.4494465068352362</v>
+        <v>1.8235990231180059</v>
       </c>
       <c r="C27">
         <v>0.05</v>
@@ -1982,7 +1982,7 @@
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" si="4"/>
-        <v>1.6194637478740994</v>
+        <v>2.1262039133007273</v>
       </c>
       <c r="C28">
         <v>0.06</v>
@@ -1991,7 +1991,7 @@
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="4"/>
-        <v>1.8093744462085373</v>
+        <v>2.4654230829492185</v>
       </c>
       <c r="C29">
         <v>7.0000000000000007E-2</v>
@@ -2000,7 +2000,7 @@
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="4"/>
-        <v>2.0182058805002976</v>
+        <v>2.84100508156655</v>
       </c>
       <c r="C30">
         <v>0.08</v>
@@ -2009,7 +2009,7 @@
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="4"/>
-        <v>2.2454560957750882</v>
+        <v>3.2531663593572722</v>
       </c>
       <c r="C31">
         <v>0.09</v>
@@ -2018,7 +2018,7 @@
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="4"/>
-        <v>2.4909141662866023</v>
+        <v>3.7023393565155454</v>
       </c>
       <c r="C32">
         <v>0.1</v>
@@ -2027,7 +2027,7 @@
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="4"/>
-        <v>2.7545468460991565</v>
+        <v>4.1890403644633087</v>
       </c>
       <c r="C33">
         <v>0.11</v>
@@ -2036,7 +2036,7 @@
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="4"/>
-        <v>3.0364275503232916</v>
+        <v>4.7138000369698672</v>
       </c>
       <c r="C34">
         <v>0.12</v>
@@ -2045,7 +2045,7 @@
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="4"/>
-        <v>3.3366916522379588</v>
+        <v>5.2771276120905464</v>
       </c>
       <c r="C35">
         <v>0.13</v>
@@ -2054,7 +2054,7 @@
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="4"/>
-        <v>3.6555081538581038</v>
+        <v>5.8794936973779865</v>
       </c>
       <c r="C36">
         <v>0.14000000000000001</v>
@@ -2063,7 +2063,7 @@
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="4"/>
-        <v>3.9930616616098176</v>
+        <v>6.521323391474553</v>
       </c>
       <c r="C37">
         <v>0.15</v>
@@ -2072,7 +2072,7 @@
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="4"/>
-        <v>4.3495409450357823</v>
+        <v>7.2029951267339349</v>
       </c>
       <c r="C38">
         <v>0.16</v>
@@ -2081,7 +2081,7 @@
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="4"/>
-        <v>4.7251317618853435</v>
+        <v>7.9248425818200712</v>
       </c>
       <c r="C39">
         <v>0.17</v>
@@ -2090,7 +2090,7 @@
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="4"/>
-        <v>5.1200124808325365</v>
+        <v>8.6871581223150045</v>
       </c>
       <c r="C40">
         <v>0.18</v>
@@ -2099,7 +2099,7 @@
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="4"/>
-        <v>5.5343515527420681</v>
+        <v>9.4901968726569734</v>
       </c>
       <c r="C41">
         <v>0.19</v>
@@ -2108,7 +2108,7 @@
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="4"/>
-        <v>5.9683062062900349</v>
+        <v>10.334180906150753</v>
       </c>
       <c r="C42">
         <v>0.2</v>
@@ -2117,7 +2117,7 @@
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="4"/>
-        <v>6.4220219511926198</v>
+        <v>11.219303270248957</v>
       </c>
       <c r="C43">
         <v>0.21</v>
@@ -2126,7 +2126,7 @@
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="4"/>
-        <v>6.8956326075225718</v>
+        <v>12.14573170305537</v>
       </c>
       <c r="C44">
         <v>0.22</v>
@@ -2135,7 +2135,7 @@
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="4"/>
-        <v>7.3892606694363563</v>
+        <v>13.11361197979598</v>
       </c>
       <c r="C45">
         <v>0.23</v>
@@ -2144,7 +2144,7 @@
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="4"/>
-        <v>7.9030178723229181</v>
+        <v>14.123070876323018</v>
       </c>
       <c r="C46">
         <v>0.24</v>
@@ -2153,7 +2153,7 @@
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="4"/>
-        <v>8.437005873940203</v>
+        <v>15.174218763754375</v>
       </c>
       <c r="C47">
         <v>0.25</v>
@@ -2162,7 +2162,7 @@
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="4"/>
-        <v>8.9913169888567257</v>
+        <v>16.267151862324532</v>
       </c>
       <c r="C48">
         <v>0.26</v>
@@ -2171,7 +2171,7 @@
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="4"/>
-        <v>9.5660349355481671</v>
+        <v>17.401954188592264</v>
       </c>
       <c r="C49">
         <v>0.27</v>
@@ -2180,7 +2180,7 @@
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="4"/>
-        <v>10.161235569508495</v>
+        <v>18.578699231558101</v>
       </c>
       <c r="C50">
         <v>0.28000000000000003</v>
@@ -2189,7 +2189,7 @@
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="4"/>
-        <v>10.776987585534668</v>
+        <v>19.797451392022275</v>
       </c>
       <c r="C51">
         <v>0.28999999999999998</v>
@@ -2198,7 +2198,7 @@
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="4"/>
-        <v>11.413353179175537</v>
+        <v>21.05826721692047</v>
       </c>
       <c r="C52">
         <v>0.3</v>
@@ -2207,7 +2207,7 @@
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="4"/>
-        <v>12.070388662062026</v>
+        <v>22.361196457177506</v>
       </c>
       <c r="C53">
         <v>0.31</v>
@@ -2216,7 +2216,7 @@
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="4"/>
-        <v>12.748145029064807</v>
+        <v>23.706282974273009</v>
       </c>
       <c r="C54">
         <v>0.32</v>
@@ -2225,7 +2225,7 @@
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="4"/>
-        <v>13.446668477388794</v>
+        <v>25.093565517475422</v>
       </c>
       <c r="C55">
         <v>0.33</v>
@@ -2234,7 +2234,7 @@
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="4"/>
-        <v>14.166000879119942</v>
+        <v>26.523078390706893</v>
       </c>
       <c r="C56">
         <v>0.34</v>
@@ -2243,7 +2243,7 @@
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="4"/>
-        <v>14.906180209610721</v>
+        <v>27.994852025310852</v>
       </c>
       <c r="C57">
         <v>0.35</v>
@@ -2252,7 +2252,7 @@
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="4"/>
-        <v>15.667240934586561</v>
+        <v>29.50891347262257</v>
       </c>
       <c r="C58">
         <v>0.36</v>
@@ -2261,7 +2261,7 @@
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59">
         <f t="shared" si="4"/>
-        <v>16.449214359091258</v>
+        <v>31.065286828179651</v>
       </c>
       <c r="C59">
         <v>0.37</v>
@@ -2270,7 +2270,7 @@
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60">
         <f t="shared" si="4"/>
-        <v>17.252128941448689</v>
+        <v>32.663993597632341</v>
       </c>
       <c r="C60">
         <v>0.38</v>
@@ -2279,7 +2279,7 @@
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61">
         <f t="shared" si="4"/>
-        <v>18.076010575359618</v>
+        <v>34.305053012892074</v>
       </c>
       <c r="C61">
         <v>0.39</v>
@@ -2288,7 +2288,7 @@
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62">
         <f t="shared" si="4"/>
-        <v>18.920882843119436</v>
+        <v>35.988482305761558</v>
       </c>
       <c r="C62">
         <v>0.4</v>
@@ -2297,7 +2297,7 @@
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63">
         <f t="shared" si="4"/>
-        <v>19.786767242764668</v>
+        <v>37.714296945189908</v>
       </c>
       <c r="C63">
         <v>0.41</v>
@@ -2306,7 +2306,7 @@
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64">
         <f t="shared" si="4"/>
-        <v>20.673683391754402</v>
+        <v>39.48251084336583</v>
       </c>
       <c r="C64">
         <v>0.42</v>
@@ -2315,7 +2315,7 @@
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <f t="shared" si="4"/>
-        <v>21.581649209581656</v>
+        <v>41.29313653507397</v>
       </c>
       <c r="C65">
         <v>0.43</v>
@@ -2324,7 +2324,7 @@
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <f t="shared" si="4"/>
-        <v>22.510681081499328</v>
+        <v>43.14618533407517</v>
       </c>
       <c r="C66">
         <v>0.44</v>
@@ -2333,7 +2333,7 @@
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <f>1/2+(1/2)*C67^2*$D$22+(1/2)*SQRT(1+6*C67^2*$D$22+(C67^4)*$D$22^2)</f>
-        <v>23.460794005341434</v>
+        <v>45.041667469709225</v>
       </c>
       <c r="C67">
         <v>0.45</v>
